--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="1562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="1562">
   <si>
     <t>类型</t>
   </si>
@@ -16556,10 +16556,10 @@
         <v>224</v>
       </c>
       <c r="C17">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D17">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -16568,13 +16568,13 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -16585,17 +16585,13 @@
       <c r="M17">
         <v>0</v>
       </c>
-      <c r="N17" t="s">
-        <v>316</v>
-      </c>
-      <c r="O17">
-        <v>2.5</v>
-      </c>
+      <c r="N17"/>
+      <c r="O17"/>
       <c r="P17">
         <v>530</v>
       </c>
       <c r="Q17" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -16604,10 +16600,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:21">

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="1608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="1609">
   <si>
     <t>类型</t>
   </si>
@@ -4806,6 +4806,9 @@
   </si>
   <si>
     <t>Full.</t>
+  </si>
+  <si>
+    <t>Mech</t>
   </si>
   <si>
     <t>Id</t>
@@ -6469,7 +6472,7 @@
         <v>25</v>
       </c>
       <c r="T8">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" s="19" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -6531,7 +6534,7 @@
         <v>15</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:20">
@@ -6593,7 +6596,7 @@
         <v>20</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:20">
@@ -6652,7 +6655,7 @@
         <v>60</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:20">
@@ -6714,7 +6717,7 @@
         <v>12</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" spans="1:20">
@@ -6776,7 +6779,7 @@
         <v>30</v>
       </c>
       <c r="T13">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" spans="1:20">
@@ -6838,7 +6841,7 @@
         <v>15</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:20">
@@ -6900,7 +6903,7 @@
         <v>12</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:20">
@@ -6962,7 +6965,7 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1" spans="1:20">
@@ -7024,7 +7027,7 @@
         <v>30</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -7068,7 +7071,7 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:20">
@@ -7130,7 +7133,7 @@
         <v>45</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1" spans="1:20">
@@ -7192,7 +7195,7 @@
         <v>20</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1" spans="1:20">
@@ -7254,7 +7257,7 @@
         <v>13</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1" spans="1:20">
@@ -7316,7 +7319,7 @@
         <v>25</v>
       </c>
       <c r="T22">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -7378,7 +7381,7 @@
         <v>50</v>
       </c>
       <c r="T23">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7440,7 +7443,7 @@
         <v>400</v>
       </c>
       <c r="T24">
-        <v>200</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7502,7 +7505,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>50</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7558,7 +7561,7 @@
         <v>50</v>
       </c>
       <c r="T26">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7620,7 +7623,7 @@
         <v>300</v>
       </c>
       <c r="T27">
-        <v>150</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7682,7 +7685,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7744,7 +7747,7 @@
         <v>200</v>
       </c>
       <c r="T29">
-        <v>100</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7806,7 +7809,7 @@
         <v>150</v>
       </c>
       <c r="T30">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7868,7 +7871,7 @@
         <v>150</v>
       </c>
       <c r="T31">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7930,7 +7933,7 @@
         <v>80</v>
       </c>
       <c r="T32">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7992,7 +7995,7 @@
         <v>120</v>
       </c>
       <c r="T33">
-        <v>60</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -8054,7 +8057,7 @@
         <v>120</v>
       </c>
       <c r="T34">
-        <v>60</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -8101,7 +8104,7 @@
         <v>15</v>
       </c>
       <c r="T35">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -8157,7 +8160,7 @@
         <v>15</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -8213,7 +8216,7 @@
         <v>12</v>
       </c>
       <c r="T37">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -8272,7 +8275,7 @@
         <v>12</v>
       </c>
       <c r="T38">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" s="19" customFormat="1" spans="1:20">
@@ -8331,7 +8334,7 @@
         <v>15</v>
       </c>
       <c r="T39">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:20">
@@ -8391,7 +8394,7 @@
         <v>20</v>
       </c>
       <c r="T40">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -8450,7 +8453,7 @@
         <v>25</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -8509,7 +8512,7 @@
         <v>10</v>
       </c>
       <c r="T42">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -8568,7 +8571,7 @@
         <v>20</v>
       </c>
       <c r="T43">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -8627,7 +8630,7 @@
         <v>30</v>
       </c>
       <c r="T44">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -8686,7 +8689,7 @@
         <v>45</v>
       </c>
       <c r="T45">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -8745,7 +8748,7 @@
         <v>25</v>
       </c>
       <c r="T46">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -9707,7 +9710,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C406"/>
+  <dimension ref="A1:C407"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="32.875" style="1" customWidth="1"/>
@@ -14179,6 +14182,17 @@
       </c>
       <c r="C406" t="s">
         <v>1567</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3">
+      <c r="A407" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>1568</v>
       </c>
     </row>
   </sheetData>
@@ -14202,24 +14216,24 @@
         <v>208</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -14239,7 +14253,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -14259,7 +14273,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -14300,10 +14314,10 @@
         <v>349</v>
       </c>
       <c r="D1" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="E1" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -14751,31 +14765,31 @@
         <v>349</v>
       </c>
       <c r="C1" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="D1" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="E1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="F1" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="G1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="H1" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="I1" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="J1" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="K1" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -14810,7 +14824,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -14845,7 +14859,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -14880,7 +14894,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -14915,7 +14929,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -14950,7 +14964,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -14985,7 +14999,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -15020,7 +15034,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -15055,7 +15069,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -15090,7 +15104,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -15125,7 +15139,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -15160,7 +15174,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -15195,7 +15209,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -15230,7 +15244,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -15265,7 +15279,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -15300,7 +15314,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -15335,7 +15349,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
   </sheetData>
@@ -15355,7 +15369,7 @@
         <v>349</v>
       </c>
       <c r="B1" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -15399,13 +15413,13 @@
         <v>349</v>
       </c>
       <c r="B1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D1" t="s">
         <v>1582</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1604</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1581</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -15537,13 +15551,13 @@
         <v>349</v>
       </c>
       <c r="B1" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="C1" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="D1" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -16023,10 +16037,10 @@
         <v>228</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="E18">
         <v>308</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -16046,7 +16046,7 @@
         <v>308</v>
       </c>
       <c r="F18">
-        <v>200</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:6">

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -18384,7 +18384,7 @@
         <v>228</v>
       </c>
       <c r="C17">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -19793,7 +19793,7 @@
         <v>1</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41">
         <v>0</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -6073,6 +6073,7 @@
     <col min="14" max="15" width="21.625" style="1" customWidth="1"/>
     <col min="16" max="17" width="14.625" style="1" customWidth="1"/>
     <col min="18" max="18" width="19.125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="14" customFormat="1" spans="1:20">
@@ -18428,7 +18429,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="b">
         <v>1</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="1" r:id="rId1"/>
@@ -6553,7 +6553,7 @@
         <v>15</v>
       </c>
       <c r="T9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1" spans="1:20">
@@ -6615,7 +6615,7 @@
         <v>20</v>
       </c>
       <c r="T10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1" spans="1:20">
@@ -6860,7 +6860,7 @@
         <v>15</v>
       </c>
       <c r="T14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1" spans="1:20">
@@ -6922,7 +6922,7 @@
         <v>12</v>
       </c>
       <c r="T15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" spans="1:20">
@@ -7090,7 +7090,7 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1" spans="1:20">
@@ -7338,7 +7338,7 @@
         <v>25</v>
       </c>
       <c r="T22">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -7400,7 +7400,7 @@
         <v>50</v>
       </c>
       <c r="T23">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7524,7 +7524,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7580,7 +7580,7 @@
         <v>50</v>
       </c>
       <c r="T26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7704,7 +7704,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7766,7 +7766,7 @@
         <v>200</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7890,7 +7890,7 @@
         <v>150</v>
       </c>
       <c r="T31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -7952,7 +7952,7 @@
         <v>80</v>
       </c>
       <c r="T32">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" s="26" customFormat="1" ht="14.25" customHeight="1" spans="1:20">
@@ -8179,7 +8179,7 @@
         <v>15</v>
       </c>
       <c r="T36">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -8235,7 +8235,7 @@
         <v>12</v>
       </c>
       <c r="T37">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -8353,7 +8353,7 @@
         <v>15</v>
       </c>
       <c r="T39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" spans="1:20">
@@ -8413,7 +8413,7 @@
         <v>20</v>
       </c>
       <c r="T40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -8590,7 +8590,7 @@
         <v>20</v>
       </c>
       <c r="T43">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -8767,7 +8767,7 @@
         <v>25</v>
       </c>
       <c r="T46">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:20">
